--- a/artfynd/A 25369-2024 artfynd.xlsx
+++ b/artfynd/A 25369-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>315058</v>
       </c>
       <c r="B2" t="n">
-        <v>89391</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487102.1715228525</v>
+        <v>487102</v>
       </c>
       <c r="R2" t="n">
-        <v>6985115.380258155</v>
+        <v>6985115</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1995-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1995-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,53 +787,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90838758</v>
+        <v>315060</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blekabäcken, söder om Tandsbyn, Jmt</t>
+          <t>(18E7j01), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487225.8927604913</v>
+        <v>487201</v>
       </c>
       <c r="R3" t="n">
-        <v>6985098.986565688</v>
+        <v>6985208</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-10-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-10-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>180479011 / PHE FERF / Enstaka-sparsam (1)  / ABR / OBJ.AREA:2,6 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,26 +873,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Via Niklas Lönnell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
     </row>
@@ -926,12 +896,7 @@
         <v>90838759</v>
       </c>
       <c r="B4" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487225.8927604913</v>
+        <v>487226</v>
       </c>
       <c r="R4" t="n">
-        <v>6985098.986565688</v>
+        <v>6985099</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,19 +961,9 @@
           <t>2019-08-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,12 +1002,7 @@
         <v>91133380</v>
       </c>
       <c r="B5" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487146.0692882849</v>
+        <v>487146</v>
       </c>
       <c r="R5" t="n">
-        <v>6985052.944818175</v>
+        <v>6985053</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,19 +1067,9 @@
           <t>2019-08-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,15 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91133381</v>
+        <v>5062558</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,17 +1136,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>(18E7j01), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487146.0692882849</v>
+        <v>487201</v>
       </c>
       <c r="R6" t="n">
-        <v>6985052.944818175</v>
+        <v>6985208</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,22 +1170,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-08-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-10-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-10-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>180479011 / HEPA NOB / Tämligen allmän (2)  / ABR / OBJ.AREA:2,6 ha</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,24 +1191,231 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>90838758</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blekabäcken, söder om Tandsbyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>487226</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6985099</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-08-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-08-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Via Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>91133381</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Halbodarna_SÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>487146</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6985053</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-08-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-08-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>

--- a/artfynd/A 25369-2024 artfynd.xlsx
+++ b/artfynd/A 25369-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/315058</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/315060</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90838759</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91133380</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5062558</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90838758</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,8 +1455,22 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91133381</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>